--- a/public/downloads/SeitzA2016.xlsx
+++ b/public/downloads/SeitzA2016.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>OH</t>
   </si>
   <si>
-    <t>O</t>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>24</v>
       </c>
       <c r="N3" s="5">
-        <v>312.6673455238342</v>
+        <v>312667.3455238342</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03416009456176491</v>
+        <v>34.16009456176491</v>
       </c>
       <c r="P3" s="5">
         <v>9153</v>
@@ -709,10 +732,10 @@
         <v>24</v>
       </c>
       <c r="N4" s="5">
-        <v>697.4205570220947</v>
+        <v>697420.5570220947</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06362165271137518</v>
+        <v>63.62165271137518</v>
       </c>
       <c r="P4" s="5">
         <v>10962</v>
@@ -759,10 +782,10 @@
         <v>24</v>
       </c>
       <c r="N5" s="5">
-        <v>892.7476062774658</v>
+        <v>892747.6062774658</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1565125536952079</v>
+        <v>156.5125536952079</v>
       </c>
       <c r="P5" s="5">
         <v>5704</v>
@@ -809,10 +832,10 @@
         <v>24</v>
       </c>
       <c r="N6" s="5">
-        <v>790.6975481510162</v>
+        <v>790697.5481510162</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08579617492958075</v>
+        <v>85.79617492958074</v>
       </c>
       <c r="P6" s="5">
         <v>9216</v>
@@ -859,10 +882,10 @@
         <v>24</v>
       </c>
       <c r="N7" s="5">
-        <v>1602.273811101913</v>
+        <v>1602273.811101913</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2948065889791929</v>
+        <v>294.806588979193</v>
       </c>
       <c r="P7" s="5">
         <v>5435</v>
@@ -909,10 +932,10 @@
         <v>24</v>
       </c>
       <c r="N8" s="5">
-        <v>165.8292298316956</v>
+        <v>165829.2298316956</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01960851718478131</v>
+        <v>19.60851718478131</v>
       </c>
       <c r="P8" s="5">
         <v>8457</v>
@@ -959,10 +982,10 @@
         <v>24</v>
       </c>
       <c r="N9" s="5">
-        <v>251.2611198425293</v>
+        <v>251261.1198425293</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03001566358171417</v>
+        <v>30.01566358171417</v>
       </c>
       <c r="P9" s="5">
         <v>8371</v>
@@ -1009,10 +1032,10 @@
         <v>24</v>
       </c>
       <c r="N10" s="5">
-        <v>759.8395886421204</v>
+        <v>759839.5886421204</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1020603879975984</v>
+        <v>102.0603879975984</v>
       </c>
       <c r="P10" s="5">
         <v>7445</v>
@@ -1059,10 +1082,10 @@
         <v>24</v>
       </c>
       <c r="N11" s="5">
-        <v>309.0712113380432</v>
+        <v>309071.2113380432</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04226325876357763</v>
+        <v>42.26325876357763</v>
       </c>
       <c r="P11" s="5">
         <v>7313</v>
@@ -1109,10 +1132,10 @@
         <v>24</v>
       </c>
       <c r="N12" s="5">
-        <v>131.7690677642822</v>
+        <v>131769.0677642822</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02606707571993714</v>
+        <v>26.06707571993714</v>
       </c>
       <c r="P12" s="5">
         <v>5055</v>
@@ -1159,10 +1182,10 @@
         <v>24</v>
       </c>
       <c r="N13" s="5">
-        <v>548.1652932167053</v>
+        <v>548165.2932167053</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07509113605708292</v>
+        <v>75.09113605708292</v>
       </c>
       <c r="P13" s="5">
         <v>7300</v>
@@ -1209,10 +1232,10 @@
         <v>24</v>
       </c>
       <c r="N14" s="5">
-        <v>1421.125238180161</v>
+        <v>1421125.238180161</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3917103743605735</v>
+        <v>391.7103743605735</v>
       </c>
       <c r="P14" s="5">
         <v>3628</v>
@@ -1259,10 +1282,10 @@
         <v>24</v>
       </c>
       <c r="N15" s="5">
-        <v>2687.890991449356</v>
+        <v>2687890.991449356</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4237570536732392</v>
+        <v>423.7570536732392</v>
       </c>
       <c r="P15" s="5">
         <v>6343</v>
@@ -1309,10 +1332,10 @@
         <v>24</v>
       </c>
       <c r="N16" s="5">
-        <v>730.6095638275146</v>
+        <v>730609.5638275146</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1002758116699855</v>
+        <v>100.2758116699855</v>
       </c>
       <c r="P16" s="5">
         <v>7286</v>
@@ -1359,10 +1382,10 @@
         <v>24</v>
       </c>
       <c r="N17" s="5">
-        <v>1582.758538007736</v>
+        <v>1582758.538007736</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1000859072978207</v>
+        <v>100.0859072978207</v>
       </c>
       <c r="P17" s="5">
         <v>15814</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2974785953578621</v>
+        <v>0.2347302920293476</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2626328610892226</v>
+        <v>0.1904338726027489</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2422084744544546</v>
+        <v>0.2112892204180057</v>
       </c>
       <c r="E3" s="4">
-        <v>67.59353741496599</v>
+        <v>61.37755102040816</v>
       </c>
       <c r="F3" s="4">
-        <v>59.05620805369137</v>
+        <v>57.6258389261745</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2347302920293476</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1904338726027489</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2992657576621986</v>
+        <v>0.2116350063653153</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1936086660143506</v>
+        <v>0.09016117663106403</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2297539379092051</v>
+        <v>0.07692053749607583</v>
       </c>
       <c r="E4" s="4">
-        <v>68.22278911564625</v>
+        <v>60.21683673469388</v>
       </c>
       <c r="F4" s="4">
-        <v>57.62304250559282</v>
+        <v>55.91862416107382</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2116350063653153</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09016117663106403</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4280388034332644</v>
+        <v>0.1575116556800484</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3025220695237508</v>
+        <v>0.09236480692025333</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3380002615536853</v>
+        <v>0.1424270705333907</v>
       </c>
       <c r="E5" s="4">
-        <v>68.38010204081633</v>
+        <v>60.63775510204081</v>
       </c>
       <c r="F5" s="4">
-        <v>60.49776286353479</v>
+        <v>52.35318791946309</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1575116556800484</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09236480692025333</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1699,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1718,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1760,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,107 +1791,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3241437052501196</v>
+        <v>0.7146667485199805</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2058256161053955</v>
+        <v>0.7384095010006315</v>
       </c>
       <c r="D3" s="4">
-        <v>0.128384367158988</v>
+        <v>0.6744350438080664</v>
       </c>
       <c r="E3" s="4">
-        <v>60.32312925170068</v>
+        <v>57.18962585034013</v>
       </c>
       <c r="F3" s="4">
-        <v>41.52265100671139</v>
+        <v>58.43400447427297</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7146667485199805</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7384095010006315</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2638931694110955</v>
+        <v>0.492042528772797</v>
       </c>
       <c r="C4" s="4">
-        <v>0.04532345846407715</v>
+        <v>0.4248519086199134</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1411739093892576</v>
+        <v>0.3683528772835392</v>
       </c>
       <c r="E4" s="4">
-        <v>65.5952380952381</v>
+        <v>60.00425170068028</v>
       </c>
       <c r="F4" s="4">
-        <v>56.84423937360175</v>
+        <v>56.22343400447425</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.492042528772797</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4248519086199134</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2995748532064844</v>
+        <v>0.4217845599610962</v>
       </c>
       <c r="C5" s="4">
-        <v>0.0383089154818067</v>
+        <v>0.4765997688541699</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1873253972348584</v>
+        <v>0.4526928148645606</v>
       </c>
       <c r="E5" s="4">
-        <v>70.89285714285714</v>
+        <v>57.49574829931973</v>
       </c>
       <c r="F5" s="4">
-        <v>62.10989932885904</v>
+        <v>48.87444071588378</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -1782,23 +1950,39 @@
         <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4217845599610962</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4765997688541699</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1993,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2012,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2054,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2085,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6251514770608697</v>
+        <v>0.4280388034332644</v>
       </c>
       <c r="C3" s="4">
-        <v>0.463007323632084</v>
+        <v>0.3025220695237508</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4246227063756738</v>
+        <v>0.3380002615536853</v>
       </c>
       <c r="E3" s="4">
-        <v>75.75680272108842</v>
+        <v>68.38010204081633</v>
       </c>
       <c r="F3" s="4">
-        <v>71.12555928411633</v>
+        <v>60.49776286353479</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="P3" s="4">
+        <v>0.4280388034332644</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3025220695237508</v>
+      </c>
+      <c r="R3" s="5">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3947821684832913</v>
+        <v>0.2992657576621986</v>
       </c>
       <c r="C4" s="4">
-        <v>0.197587138310311</v>
+        <v>0.1936086660143506</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2409305699820858</v>
+        <v>0.2297539379092051</v>
       </c>
       <c r="E4" s="4">
-        <v>76.11394557823128</v>
+        <v>68.22278911564625</v>
       </c>
       <c r="F4" s="4">
-        <v>73.37248322147654</v>
+        <v>57.62304250559282</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2992657576621986</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1936086660143506</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2732808942832117</v>
+        <v>0.2974785953578621</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2508884692519319</v>
+        <v>0.2626328610892226</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2550998683013086</v>
+        <v>0.2422084744544546</v>
       </c>
       <c r="E5" s="4">
-        <v>77.25340136054423</v>
+        <v>67.59353741496599</v>
       </c>
       <c r="F5" s="4">
-        <v>78.03551454138702</v>
+        <v>59.05620805369137</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>6</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="P5" s="4">
+        <v>0.2974785953578621</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2626328610892226</v>
+      </c>
+      <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2287,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2306,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2348,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2379,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6887282647710595</v>
+        <v>0.2995748532064844</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5355009067979345</v>
+        <v>0.0383089154818067</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4797612943273339</v>
+        <v>0.1873253972348584</v>
       </c>
       <c r="E3" s="4">
-        <v>59.61734693877551</v>
+        <v>70.89285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>49.78887024608493</v>
+        <v>62.10989932885904</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2995748532064844</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0383089154818067</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3066714358101321</v>
+        <v>0.2638931694110955</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3948790884656579</v>
+        <v>0.04532345846407715</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3369741567130429</v>
+        <v>0.1411739093892576</v>
       </c>
       <c r="E4" s="4">
-        <v>68.82227891156462</v>
+        <v>65.5952380952381</v>
       </c>
       <c r="F4" s="4">
-        <v>63.28719239373602</v>
+        <v>56.84423937360175</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2638931694110955</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04532345846407715</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2977859199169263</v>
+        <v>0.3241437052501196</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2223250253156933</v>
+        <v>0.2058256161053955</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2403369898833398</v>
+        <v>0.128384367158988</v>
       </c>
       <c r="E5" s="4">
-        <v>67.61904761904761</v>
+        <v>60.32312925170068</v>
       </c>
       <c r="F5" s="4">
-        <v>60.38171140939598</v>
+        <v>41.52265100671139</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3241437052501196</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2058256161053955</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2581,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2600,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2642,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2673,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.100712015289757</v>
+        <v>0.2732808942832117</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1086903214428905</v>
+        <v>0.2508884692519319</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1049736021079546</v>
+        <v>0.2550998683013086</v>
       </c>
       <c r="E3" s="4">
-        <v>89.46003401360545</v>
+        <v>77.25340136054423</v>
       </c>
       <c r="F3" s="4">
-        <v>88.81711409395973</v>
+        <v>78.03551454138702</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2508884692519319</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07834240210854172</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07459996943634932</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.0629002985988206</v>
+        <v>0.3947821684832913</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06621375082960068</v>
+        <v>0.197587138310311</v>
       </c>
       <c r="D4" s="4">
-        <v>0.07654452635685635</v>
+        <v>0.2409305699820858</v>
       </c>
       <c r="E4" s="4">
-        <v>89.5578231292517</v>
+        <v>76.11394557823128</v>
       </c>
       <c r="F4" s="4">
-        <v>89.06599552572708</v>
+        <v>73.37248322147654</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3947821684832913</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.197587138310311</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.100191315736649</v>
+        <v>0.6251514770608697</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08227380000635888</v>
+        <v>0.463007323632084</v>
       </c>
       <c r="D5" s="4">
-        <v>0.08678818045825498</v>
+        <v>0.4246227063756738</v>
       </c>
       <c r="E5" s="4">
-        <v>90.87159863945578</v>
+        <v>75.75680272108842</v>
       </c>
       <c r="F5" s="4">
-        <v>90.81655480984341</v>
+        <v>71.12555928411633</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.463007323632084</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1984939435399554</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0410867133359929</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2879,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2887,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2898,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2940,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2971,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8603404194634487</v>
+        <v>0.2977859199169263</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8972484856018449</v>
+        <v>0.2223250253156933</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8858462788682724</v>
+        <v>0.2403369898833398</v>
       </c>
       <c r="E3" s="4">
-        <v>75.8843537414966</v>
+        <v>67.61904761904761</v>
       </c>
       <c r="F3" s="4">
-        <v>65.1524049217002</v>
+        <v>60.38171140939598</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -2566,34 +3030,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2977859199169263</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2223250253156933</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4947910954991338</v>
+        <v>0.3066714358101321</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6336829433748221</v>
+        <v>0.3948790884656579</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6030242272372608</v>
+        <v>0.3369741567130429</v>
       </c>
       <c r="E4" s="4">
-        <v>76.37329931972789</v>
+        <v>68.82227891156462</v>
       </c>
       <c r="F4" s="4">
-        <v>68.12360178970917</v>
+        <v>63.28719239373602</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>5</v>
@@ -2607,25 +3087,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3066714358101321</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3948790884656579</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3971917434089165</v>
+        <v>0.6887282647710595</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4337516128446567</v>
+        <v>0.5355009067979345</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4335854406393915</v>
+        <v>0.4797612943273339</v>
       </c>
       <c r="E5" s="4">
-        <v>76.34778911564626</v>
+        <v>59.61734693877551</v>
       </c>
       <c r="F5" s="4">
-        <v>70.77321029082758</v>
+        <v>49.78887024608493</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -2648,9 +3144,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6887282647710595</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5355009067979345</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3173,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3192,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3234,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3265,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6231674707908241</v>
+        <v>0.100191315736649</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5521292324434217</v>
+        <v>0.08227380000635888</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3248013935465779</v>
+        <v>0.08678818045825498</v>
       </c>
       <c r="E3" s="4">
-        <v>71.70918367346938</v>
+        <v>90.87159863945578</v>
       </c>
       <c r="F3" s="4">
-        <v>63.76398210290827</v>
+        <v>90.81655480984341</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08227380000635888</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06381696323234715</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05245651143092235</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5471457655822216</v>
+        <v>0.0629002985988206</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4697553928489419</v>
+        <v>0.06621375082960068</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2683362535481559</v>
+        <v>0.07654452635685635</v>
       </c>
       <c r="E4" s="4">
-        <v>66.32227891156462</v>
+        <v>89.5578231292517</v>
       </c>
       <c r="F4" s="4">
-        <v>58.80592841163312</v>
+        <v>89.06599552572708</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.01050381925150314</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06158584899811838</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06321097710715483</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4809521903358602</v>
+        <v>0.100712015289757</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3466720253088892</v>
+        <v>0.1086903214428905</v>
       </c>
       <c r="D5" s="4">
-        <v>0.255077609892969</v>
+        <v>0.1049736021079546</v>
       </c>
       <c r="E5" s="4">
-        <v>65.78656462585036</v>
+        <v>89.46003401360545</v>
       </c>
       <c r="F5" s="4">
-        <v>56.63450782997771</v>
+        <v>88.81711409395973</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.09696505723900341</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06833533558724547</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07065449995382621</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3473,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3481,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3492,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3534,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3565,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5400244363170197</v>
+        <v>0.3971917434089165</v>
       </c>
       <c r="C3" s="4">
-        <v>0.670432771571955</v>
+        <v>0.4337516128446567</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6351303376775173</v>
+        <v>0.4335854406393915</v>
       </c>
       <c r="E3" s="4">
-        <v>71.92176870748277</v>
+        <v>76.34778911564626</v>
       </c>
       <c r="F3" s="4">
-        <v>61.30592841163416</v>
+        <v>70.77321029082758</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -2978,105 +3610,153 @@
         <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3971917434089165</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4337516128446567</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3806775359031935</v>
+        <v>0.4947910954991338</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5059680206467284</v>
+        <v>0.6336829433748221</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4696961768622832</v>
+        <v>0.6030242272372608</v>
       </c>
       <c r="E4" s="4">
-        <v>74.7321428571433</v>
+        <v>76.37329931972789</v>
       </c>
       <c r="F4" s="4">
-        <v>67.59088366890509</v>
+        <v>68.12360178970917</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4947910954991338</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6336829433748221</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.465669765097217</v>
+        <v>0.8603404194634487</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5056276524618853</v>
+        <v>0.8972484856018449</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3979104514159326</v>
+        <v>0.8858462788682724</v>
       </c>
       <c r="E5" s="4">
-        <v>73.7372448979594</v>
+        <v>75.8843537414966</v>
       </c>
       <c r="F5" s="4">
-        <v>67.94882550335609</v>
+        <v>65.1524049217002</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8603404194634487</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8972484856018449</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3767,1458 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4809521903358602</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3466720253088892</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.255077609892969</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.78656462585036</v>
+      </c>
+      <c r="F3" s="4">
+        <v>56.63450782997771</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4809521903358602</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3466720253088892</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5471457655822216</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4697553928489419</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2683362535481559</v>
+      </c>
+      <c r="E4" s="4">
+        <v>66.32227891156462</v>
+      </c>
+      <c r="F4" s="4">
+        <v>58.80592841163312</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5471457655822216</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4697553928489419</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6231674707908241</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5521292324434217</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3248013935465779</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.70918367346938</v>
+      </c>
+      <c r="F5" s="4">
+        <v>63.76398210290827</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6231674707908241</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5521292324434217</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.465669765097217</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5056276524618853</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3979104514159326</v>
+      </c>
+      <c r="E3" s="4">
+        <v>73.7372448979594</v>
+      </c>
+      <c r="F3" s="4">
+        <v>67.94882550335609</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.465669765097217</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5056276524618853</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3806775359031935</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5059680206467284</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4696961768622832</v>
+      </c>
+      <c r="E4" s="4">
+        <v>74.7321428571433</v>
+      </c>
+      <c r="F4" s="4">
+        <v>67.59088366890509</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3806775359031935</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5059680206467284</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5400244363170197</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.670432771571955</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6351303376775173</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.92176870748277</v>
+      </c>
+      <c r="F5" s="4">
+        <v>61.30592841163416</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5400244363170197</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.670432771571955</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>75</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="F3" s="3">
+        <v>70.83333333333334</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.321869334029317</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.07975277207008302</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1869288145081825</v>
+      </c>
+      <c r="K3" s="4">
+        <v>48.74291383219961</v>
+      </c>
+      <c r="L3" s="4">
+        <v>48.55658090976907</v>
+      </c>
+      <c r="M3" s="5">
+        <v>24</v>
+      </c>
+      <c r="N3" s="5">
+        <v>312667.3455238342</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.16009456176491</v>
+      </c>
+      <c r="P3" s="5">
+        <v>9153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="F4" s="3">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="G4" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.64506261066326</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1601639888180664</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.410157774602158</v>
+      </c>
+      <c r="K4" s="4">
+        <v>58.47789115646236</v>
+      </c>
+      <c r="L4" s="4">
+        <v>55.87434750186419</v>
+      </c>
+      <c r="M4" s="5">
+        <v>24</v>
+      </c>
+      <c r="N4" s="5">
+        <v>697420.5570220947</v>
+      </c>
+      <c r="O4" s="4">
+        <v>63.62165271137518</v>
+      </c>
+      <c r="P4" s="5">
+        <v>10962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1454640041689106</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.08612344146497374</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1242122579491309</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.06575963718825</v>
+      </c>
+      <c r="L5" s="4">
+        <v>74.43139448173019</v>
+      </c>
+      <c r="M5" s="5">
+        <v>24</v>
+      </c>
+      <c r="N5" s="5">
+        <v>892747.6062774658</v>
+      </c>
+      <c r="O5" s="4">
+        <v>156.5125536952079</v>
+      </c>
+      <c r="P5" s="5">
+        <v>5704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D6" s="3">
+        <v>75</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>75</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2792720893575449</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1755338324054719</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1676778610863045</v>
+      </c>
+      <c r="K6" s="4">
+        <v>52.02522675736971</v>
+      </c>
+      <c r="L6" s="4">
+        <v>44.8564504101414</v>
+      </c>
+      <c r="M6" s="5">
+        <v>24</v>
+      </c>
+      <c r="N6" s="5">
+        <v>790697.5481510162</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.79617492958074</v>
+      </c>
+      <c r="P6" s="5">
+        <v>9216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D7" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2140284459950229</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1307468527642219</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1387519296958533</v>
+      </c>
+      <c r="K7" s="4">
+        <v>77.89257369614516</v>
+      </c>
+      <c r="L7" s="4">
+        <v>76.88105891126042</v>
+      </c>
+      <c r="M7" s="5">
+        <v>24</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1602273.811101913</v>
+      </c>
+      <c r="O7" s="4">
+        <v>294.806588979193</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2012923180249038</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1243199520513554</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1435456094824907</v>
+      </c>
+      <c r="K8" s="4">
+        <v>60.74404761904766</v>
+      </c>
+      <c r="L8" s="4">
+        <v>55.29921700223651</v>
+      </c>
+      <c r="M8" s="5">
+        <v>24</v>
+      </c>
+      <c r="N8" s="5">
+        <v>165829.2298316956</v>
+      </c>
+      <c r="O8" s="4">
+        <v>19.60851718478131</v>
+      </c>
+      <c r="P8" s="5">
+        <v>8457</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D9" s="3">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5428312790846245</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5553729708212468</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4984935786520554</v>
+      </c>
+      <c r="K9" s="4">
+        <v>58.2298752834469</v>
+      </c>
+      <c r="L9" s="4">
+        <v>54.51062639820985</v>
+      </c>
+      <c r="M9" s="5">
+        <v>24</v>
+      </c>
+      <c r="N9" s="5">
+        <v>251261.1198425293</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.01566358171417</v>
+      </c>
+      <c r="P9" s="5">
+        <v>8371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D10" s="3">
+        <v>75</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>75</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3415943854844417</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2647837054480595</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2699875579724483</v>
+      </c>
+      <c r="K10" s="4">
+        <v>68.06547619047619</v>
+      </c>
+      <c r="L10" s="4">
+        <v>59.05900447427342</v>
+      </c>
+      <c r="M10" s="5">
+        <v>24</v>
+      </c>
+      <c r="N10" s="5">
+        <v>759839.5886421204</v>
+      </c>
+      <c r="O10" s="4">
+        <v>102.0603879975984</v>
+      </c>
+      <c r="P10" s="5">
+        <v>7445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D11" s="3">
+        <v>79.16666666666666</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>79.16666666666666</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2958705759558998</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.08194172638327152</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1522945579277014</v>
+      </c>
+      <c r="K11" s="4">
+        <v>65.60374149659835</v>
+      </c>
+      <c r="L11" s="4">
+        <v>53.49226323639113</v>
+      </c>
+      <c r="M11" s="5">
+        <v>24</v>
+      </c>
+      <c r="N11" s="5">
+        <v>309071.2113380432</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.26325876357763</v>
+      </c>
+      <c r="P11" s="5">
+        <v>7313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>25</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2238728380439295</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.09622546243595362</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1297325509157737</v>
+      </c>
+      <c r="K12" s="4">
+        <v>76.37471655328785</v>
+      </c>
+      <c r="L12" s="4">
+        <v>74.17785234899354</v>
+      </c>
+      <c r="M12" s="5">
+        <v>24</v>
+      </c>
+      <c r="N12" s="5">
+        <v>131769.0677642822</v>
+      </c>
+      <c r="O12" s="4">
+        <v>26.06707571993714</v>
+      </c>
+      <c r="P12" s="5">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4310618734993727</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3842350068597619</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.3523574803079055</v>
+      </c>
+      <c r="K13" s="4">
+        <v>65.35289115646245</v>
+      </c>
+      <c r="L13" s="4">
+        <v>57.819258016406</v>
+      </c>
+      <c r="M13" s="5">
+        <v>24</v>
+      </c>
+      <c r="N13" s="5">
+        <v>548165.2932167053</v>
+      </c>
+      <c r="O13" s="4">
+        <v>75.09113605708292</v>
+      </c>
+      <c r="P13" s="5">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.06457938260590367</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.06210732949730113</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.06772768626329816</v>
+      </c>
+      <c r="K14" s="4">
+        <v>89.96315192743762</v>
+      </c>
+      <c r="L14" s="4">
+        <v>89.5665548098435</v>
+      </c>
+      <c r="M14" s="5">
+        <v>24</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1421125.238180161</v>
+      </c>
+      <c r="O14" s="4">
+        <v>391.7103743605735</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D15" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5841077527904996</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.6575457727611437</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.6408186489149749</v>
+      </c>
+      <c r="K15" s="4">
+        <v>76.20181405895691</v>
+      </c>
+      <c r="L15" s="4">
+        <v>68.0164056674124</v>
+      </c>
+      <c r="M15" s="5">
+        <v>24</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2687890.991449356</v>
+      </c>
+      <c r="O15" s="4">
+        <v>423.7570536732392</v>
+      </c>
+      <c r="P15" s="5">
+        <v>6343</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>75</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>75</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5504218089029687</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4561855502004176</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.282738418995901</v>
+      </c>
+      <c r="K16" s="4">
+        <v>67.93934240362852</v>
+      </c>
+      <c r="L16" s="4">
+        <v>59.73480611484005</v>
+      </c>
+      <c r="M16" s="5">
+        <v>24</v>
+      </c>
+      <c r="N16" s="5">
+        <v>730609.5638275146</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.2758116699855</v>
+      </c>
+      <c r="P16" s="5">
+        <v>7286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D17" s="3">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.4621239124391434</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5551712986503592</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.5009123219852444</v>
+      </c>
+      <c r="K17" s="4">
+        <v>73.46371882086176</v>
+      </c>
+      <c r="L17" s="4">
+        <v>65.61521252796501</v>
+      </c>
+      <c r="M17" s="5">
+        <v>24</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1582758.538007736</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.0859072978207</v>
+      </c>
+      <c r="P17" s="5">
+        <v>15814</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3209,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3253,13 +5379,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
         <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3822,16 +5948,16 @@
         <v>3</v>
       </c>
       <c r="K17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +5973,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>11</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>15</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>10</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>11</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>7</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>9</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>9</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>15</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>18</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>18</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>6</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>10</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>3</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6741,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6783,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6814,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4066243531532813</v>
+        <v>0.3512361475533594</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08575236276687503</v>
+        <v>0.05398671962000001</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2428522787470069</v>
+        <v>0.1798913904732812</v>
       </c>
       <c r="E3" s="4">
-        <v>46.41581632653061</v>
+        <v>50.01700680272108</v>
       </c>
       <c r="F3" s="4">
-        <v>42.17281879194633</v>
+        <v>53.78635346756158</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -3952,18 +6865,34 @@
         <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3512361475533594</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05398671962000001</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2077475013813104</v>
@@ -4001,25 +6930,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2077475013813104</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09951923382337402</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3512361475533594</v>
+        <v>0.4066243531532813</v>
       </c>
       <c r="C5" s="4">
-        <v>0.05398671962000001</v>
+        <v>0.08575236276687503</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1798913904732812</v>
+        <v>0.2428522787470069</v>
       </c>
       <c r="E5" s="4">
-        <v>50.01700680272108</v>
+        <v>46.41581632653061</v>
       </c>
       <c r="F5" s="4">
-        <v>53.78635346756158</v>
+        <v>42.17281879194633</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -4034,17 +6979,33 @@
         <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4066243531532813</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08575236276687503</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7016,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7035,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7077,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,51 +7108,85 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>3.338045426406309</v>
+        <v>1.074453666085156</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1161726254257812</v>
       </c>
       <c r="D3" s="4">
-        <v>3.288857289351865</v>
+        <v>0.8118603967370117</v>
       </c>
       <c r="E3" s="4">
-        <v>59.03486394557825</v>
+        <v>58.54166666666666</v>
       </c>
       <c r="F3" s="4">
-        <v>53.84088366890396</v>
+        <v>59.40016778523488</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>1.074453666085156</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1161726254257812</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5226887394983145</v>
@@ -4214,50 +7224,78 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5226887394983145</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2041553522103516</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.074453666085156</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1161726254257812</v>
-      </c>
+        <v>3.338045426406309</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.8118603967370117</v>
+        <v>3.288857289351865</v>
       </c>
       <c r="E5" s="4">
-        <v>58.54166666666666</v>
+        <v>59.03486394557825</v>
       </c>
       <c r="F5" s="4">
-        <v>59.40016778523488</v>
+        <v>53.84088366890396</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>3.338045426406309</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7306,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7325,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7367,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,25 +7398,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1866241029981826</v>
+        <v>0.2787276458852057</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2053590730780151</v>
+        <v>0.2628703185198254</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1922709826066881</v>
+        <v>0.2422497015371983</v>
       </c>
       <c r="E3" s="4">
-        <v>75.56972789115646</v>
+        <v>76.4795918367347</v>
       </c>
       <c r="F3" s="4">
-        <v>72.77824384787473</v>
+        <v>75.8165548098434</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -4386,10 +7457,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2628703185198254</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1520520964475809</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07524515087318774</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2356197423106665</v>
@@ -4427,25 +7516,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1280411614731699</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1939181887807796</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08730038115595214</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2787276458852057</v>
+        <v>0.1866241029981826</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2628703185198254</v>
+        <v>0.2053590730780151</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2422497015371983</v>
+        <v>0.1922709826066881</v>
       </c>
       <c r="E5" s="4">
-        <v>76.4795918367347</v>
+        <v>75.56972789115646</v>
       </c>
       <c r="F5" s="4">
-        <v>75.8165548098434</v>
+        <v>72.77824384787473</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
@@ -4468,9 +7575,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2053590730780151</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0904217272783715</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09582479236578131</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7606,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7625,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7667,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7698,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.30781264766125</v>
+        <v>0.2197433351910742</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1936095145364845</v>
+        <v>0.1437328783012499</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1487474010792188</v>
+        <v>0.2145634419340234</v>
       </c>
       <c r="E3" s="4">
-        <v>52.1471088435374</v>
+        <v>51.64115646258503</v>
       </c>
       <c r="F3" s="4">
-        <v>44.84340044742731</v>
+        <v>45.50755033557044</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>6</v>
@@ -4599,10 +7757,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2197433351910742</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1437328783012499</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3102602852203106</v>
@@ -4640,34 +7814,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3102602852203106</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1982969454441875</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2197433351910742</v>
+        <v>0.30781264766125</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1437328783012499</v>
+        <v>0.1936095145364845</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2145634419340234</v>
+        <v>0.1487474010792188</v>
       </c>
       <c r="E5" s="4">
-        <v>51.64115646258503</v>
+        <v>52.1471088435374</v>
       </c>
       <c r="F5" s="4">
-        <v>45.50755033557044</v>
+        <v>44.84340044742731</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>6</v>
@@ -4681,9 +7871,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.30781264766125</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1936095145364845</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7900,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7919,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7961,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,34 +7992,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3693656926640227</v>
+        <v>0.2184925432242517</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3158705959309033</v>
+        <v>0.2590389734417715</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3079270639043603</v>
+        <v>0.218090152267373</v>
       </c>
       <c r="E3" s="4">
-        <v>78.9795918367347</v>
+        <v>74.83418367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>77.11968680089485</v>
+        <v>74.66862416107382</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -4812,10 +8051,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2590389734417715</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08958681770176972</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06618321681019998</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2770743680933664</v>
@@ -4853,34 +8110,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.265676845430594</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1831328276192761</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04721149418489862</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2184925432242517</v>
+        <v>0.3693656926640227</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2590389734417715</v>
+        <v>0.3158705959309033</v>
       </c>
       <c r="D5" s="4">
-        <v>0.218090152267373</v>
+        <v>0.3079270639043603</v>
       </c>
       <c r="E5" s="4">
-        <v>74.83418367346938</v>
+        <v>78.9795918367347</v>
       </c>
       <c r="F5" s="4">
-        <v>74.66862416107382</v>
+        <v>77.11968680089485</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -4894,9 +8169,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3693656926640227</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3158705959309033</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8198,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1575116556800484</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.09236480692025333</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1424270705333907</v>
-      </c>
-      <c r="E3" s="4">
-        <v>60.63775510204081</v>
-      </c>
-      <c r="F3" s="4">
-        <v>52.35318791946309</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2116350063653153</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.09016117663106403</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.07692053749607583</v>
-      </c>
-      <c r="E4" s="4">
-        <v>60.21683673469388</v>
-      </c>
-      <c r="F4" s="4">
-        <v>55.91862416107382</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2347302920293476</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1904338726027489</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2112892204180057</v>
-      </c>
-      <c r="E5" s="4">
-        <v>61.37755102040816</v>
-      </c>
-      <c r="F5" s="4">
-        <v>57.6258389261745</v>
-      </c>
-      <c r="G5" s="5">
-        <v>8</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4217845599610962</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4765997688541699</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4526928148645606</v>
-      </c>
-      <c r="E3" s="4">
-        <v>57.49574829931973</v>
-      </c>
-      <c r="F3" s="4">
-        <v>48.87444071588378</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.492042528772797</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4248519086199134</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3683528772835392</v>
-      </c>
-      <c r="E4" s="4">
-        <v>60.00425170068028</v>
-      </c>
-      <c r="F4" s="4">
-        <v>56.22343400447425</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7146667485199805</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7384095010006315</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6744350438080664</v>
-      </c>
-      <c r="E5" s="4">
-        <v>57.18962585034013</v>
-      </c>
-      <c r="F5" s="4">
-        <v>58.43400447427297</v>
-      </c>
-      <c r="G5" s="5">
-        <v>8</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SeitzA2016.xlsx
+++ b/public/downloads/SeitzA2016.xlsx
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2508884692519319</v>
+        <v>-0.2246995818573633</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07834240210854172</v>
+        <v>0.08488962395718389</v>
       </c>
       <c r="Q3" s="4">
         <v>0.07459996943634932</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.463007323632084</v>
+        <v>-0.4626555827280128</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
@@ -2858,7 +2858,7 @@
         <v>0.1984939435399554</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0410867133359929</v>
+        <v>0.04101636515517866</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08227380000635888</v>
+        <v>0.07670066861458857</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
@@ -3334,7 +3334,7 @@
         <v>0.06381696323234715</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05245651143092235</v>
+        <v>0.05166034980352659</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3384,16 +3384,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01050381925150314</v>
+        <v>0.01581188027883301</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06158584899811838</v>
+        <v>0.06158584899811837</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06321097710715483</v>
+        <v>0.06245268267467913</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.09696505723900341</v>
+        <v>0.1321602193527047</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
@@ -3452,7 +3452,7 @@
         <v>0.06833533558724547</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07065449995382621</v>
+        <v>0.06562661965186889</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1454640041689106</v>
+        <v>0.1431514110101166</v>
       </c>
       <c r="I5" s="4">
-        <v>0.08612344146497374</v>
+        <v>0.08367843159405346</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1242122579491309</v>
+        <v>0.1239446502484781</v>
       </c>
       <c r="K5" s="4">
         <v>76.06575963718825</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2140284459950229</v>
+        <v>0.206991101440175</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1307468527642219</v>
+        <v>0.1271587195927781</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1387519296958533</v>
+        <v>0.142473900835082</v>
       </c>
       <c r="K7" s="4">
         <v>77.89257369614516</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2238728380439295</v>
+        <v>0.2260552453268102</v>
       </c>
       <c r="I12" s="4">
-        <v>0.09622546243595362</v>
+        <v>0.09620201304234888</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1297325509157737</v>
+        <v>0.1300350197761408</v>
       </c>
       <c r="K12" s="4">
         <v>76.37471655328785</v>
@@ -5024,10 +5024,10 @@
         <v>0.06457938260590367</v>
       </c>
       <c r="I14" s="4">
-        <v>0.06210732949730113</v>
+        <v>0.05991321737669154</v>
       </c>
       <c r="J14" s="4">
-        <v>0.06772768626329816</v>
+        <v>0.06774977546033485</v>
       </c>
       <c r="K14" s="4">
         <v>89.96315192743762</v>
@@ -7458,16 +7458,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2628703185198254</v>
+        <v>-0.2596590261119922</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1520520964475809</v>
+        <v>0.1512492733456226</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07524515087318774</v>
+        <v>0.0746028923916211</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7517,16 +7517,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1280411614731699</v>
+        <v>-0.1525809869708653</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1939181887807796</v>
+        <v>0.1877832324063557</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08730038115595214</v>
+        <v>0.08239241605641305</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2053590730780151</v>
+        <v>-0.1964350429197395</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
@@ -7585,7 +7585,7 @@
         <v>0.0904217272783715</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09582479236578131</v>
+        <v>0.09403998633412618</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -8052,16 +8052,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2590389734417715</v>
+        <v>-0.2430193792995214</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08958681770176972</v>
+        <v>0.08558191916620722</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06618321681019998</v>
+        <v>0.06297929798174998</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -8111,16 +8111,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.265676845430594</v>
+        <v>-0.2314625751726318</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1831328276192761</v>
+        <v>0.166025692490295</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04721149418489862</v>
+        <v>0.04036864013330618</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
